--- a/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Statements'!$A$1:$K$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Variables'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Statements'!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Variables'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -513,348 +513,376 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (facet statements) and which domain a kind of test goes to (routing statements). With the variable-table</t>
+          <t xml:space="preserve">  (facet statements), which domain a kind of test goes to (routing statements), and what qualifies or</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  rows of every variable the statements name.</t>
+          <t xml:space="preserve">  links the record rather than the test (record statements). With the variable-table rows of every</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  variable the statements name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Facts with citations only: nothing is classified, interpreted or decided here.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>SCOPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32 statements: 16 selected as facet, 16 as routing. 34 variables.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The selection is hand-kept in the notebook; the text is not. Selected_As records why a row was selected,</t>
+          <t>44 statements: 21 selected as facet, 19 as routing, 4 as record. 42 variables.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  The selection is hand-kept in the notebook; the text is not. Selected_As records why a row was selected,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  not what the text means. Other IG statements are not here.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SOURCE VERSIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 (2021-11-29) / SDTM v2.0 · pinned in Reference_Versions.json (repo root).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  As keys for programs: sheet Provenance.</t>
+          <t>SDTMIG v3.4 (2021-11-29) / SDTM v2.0 · pinned in Reference_Versions.json (repo root).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-31 14:39</t>
+          <t xml:space="preserve">  As keys for programs: sheet Provenance.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Notebook: sdtm-domain-reference/notebooks/SDTMIG_Statements.ipynb</t>
+          <t>Generated: 2026-10-31 22:14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Inputs: SDTMIG v3.4-FINAL_2022-07-21.pdf, SDTMIG_v3.4.csv and SDTM_v2.0.csv (CDISC, downloaded with a cdisc.org sign-in;</t>
+          <t>Notebook: sdtm-domain-reference/notebooks/SDTMIG_Statements.ipynb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  not in the repo).</t>
+          <t>Inputs: SDTMIG v3.4-FINAL_2022-07-21.pdf, SDTMIG_v3.4.csv and SDTM_v2.0.csv (CDISC, downloaded with a cdisc.org sign-in;</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  not in the repo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Quoted text © 2021 Clinical Data Interchange Standards Consortium, Inc. Exploratory work, not a CDISC product.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>KNOWN GAPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Text is as pdfminer.six extracts it, joined into one paragraph: line breaks, indentation and list layout</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  are lost; quotes, bullets and spacing around punctuation are kept as extracted (e.g. "MKHNDPOS".This).</t>
+          <t>Text is as pdfminer.six extracts it, joined into one paragraph: line breaks, indentation and list layout</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CDISC Notes are quoted from the CSV as published, including its literal \n paragraph markers.</t>
+          <t xml:space="preserve">  are lost; quotes, bullets and spacing around punctuation are kept as extracted (e.g. "MKHNDPOS".This).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Variables_Named and Domains_Named are found by pattern (see below), not read by a person. Generic --</t>
+          <t>CDISC Notes are quoted from the CSV as published, including its literal \n paragraph markers.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  forms and identifiers of no single dataset (STUDYID, USUBJID, VISITNUM, SPDEVID, NHOID) are not listed.</t>
+          <t>Variables_Named and Domains_Named are found by pattern (see below), not read by a person. Generic --</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  forms and identifiers of no single dataset (STUDYID, USUBJID, VISITNUM, SPDEVID, NHOID) are not listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Worked examples in the IG are not quoted, only Assumptions, §4.1.9 and CDISC Notes.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RS – Clinical Classifications Use Case Assumptions holds the QRS assumptions as a second numbered list</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Statements — one row per quoted statement.</t>
+          <t xml:space="preserve">  after its item 3; only items 1-3 of that block can be selected. The same --EVAL text is quoted from QS.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Variables — one row per variable in Variables_Named: the SDTMIG v3.4 variable-table row as published,</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  plus Named_In. An empty CDISC CT Codelist Code(s) means the table gives no codelist (e.g. PCTESTCD).</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SHEETS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Provenance — versions; per sheet rows, columns and a content hash.</t>
+          <t>Statements — one row per quoted statement.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Variables — one row per variable in Variables_Named: the SDTMIG v3.4 variable-table row as published,</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMNS — Statements</t>
+          <t xml:space="preserve">  plus Named_In. An empty CDISC CT Codelist Code(s) means the table gives no codelist (e.g. PCTESTCD).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Statement_ID: domain + A + assumption item (+ sub-item), e.g. IS-A7b; 4.1.9-n for the §4.1.9 passages in</t>
+          <t>Provenance — versions; per sheet rows, columns and a content hash.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  order; &lt;variable&gt;-Notes for CDISC Notes. RS-DR = RS Disease Response Use Case Assumptions.</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Selected_As: facet | routing — why the row was selected.</t>
+          <t>COLUMNS — Statements</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Source: the document and its date.</t>
+          <t>Statement_ID: domain + A + assumption item (+ sub-item), e.g. IS-A7b; 4.1.9-n for the §4.1.9 passages in</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Section: the numbered IG section; for Assumptions also the Assumptions heading.</t>
+          <t xml:space="preserve">  order; &lt;variable&gt;-Notes for CDISC Notes. RS-DR = RS Disease Response Use Case Assumptions;</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Item: assumption item and lettered sub-item. An item row holds the item's text before its first sub-item;</t>
+          <t xml:space="preserve">  RS-CC = RS Clinical Classifications Use Case Assumptions.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a sub-item row keeps its roman sub-items (e.g. 1c holds i-iv).</t>
+          <t>Selected_As: facet | routing | record — why the row was selected.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Page: page in the IG (printed page = PDF page). Empty for CDISC Notes (CSV).</t>
+          <t>Source: the document and its date.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Domain: the dataset whose Assumptions or Notes the text belongs to; empty for §4.1.9.</t>
+          <t>Section: the numbered IG section; for Assumptions also the Assumptions heading.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Variables_Named: words that are variables of the dataset their first two letters name, in the SDTMIG v3.4</t>
+          <t>Item: assumption item and lettered sub-item. An item row holds the item's text before its first sub-item;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  variable table; in order of first appearance.</t>
+          <t xml:space="preserve">  a sub-item row keeps its roman sub-items (e.g. 1c holds i-iv).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Model_Variables_Named: words not in that dataset's SDTMIG v3.4 table whose -- form is an SDTM v2.0 variable</t>
+          <t>Page: page in the IG (printed page = PDF page). Empty for CDISC Notes (CSV).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of the dataset's observation class (e.g. LBPOS and LBLOC in LB-A8: --POS and --LOC, Findings).</t>
+          <t>Domain: the dataset whose Assumptions or Notes the text belongs to; empty for §4.1.9.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Domains_Named: dataset codes written as (XX) or "XX domain"; in order of first appearance.</t>
+          <t>Variables_Named: words that are variables of the dataset their first two letters name, in the SDTMIG v3.4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Text: the statement, verbatim.</t>
+          <t xml:space="preserve">  variable table; in order of first appearance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Model_Variables_Named: words not in that dataset's SDTMIG v3.4 table whose -- form is an SDTM v2.0 variable</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>COLUMNS — Variables</t>
+          <t xml:space="preserve">  of the dataset's observation class (e.g. LBPOS and LBLOC in LB-A8: --POS and --LOC, Findings).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>The columns of SDTMIG_v3.4.csv, unchanged, plus Named_In: the Statement_IDs that name the variable.</t>
+          <t>Domains_Named: dataset codes written as (XX) or "XX domain"; in order of first appearance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Text: the statement, verbatim.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>READING</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>COLUMNS — Variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>The columns of SDTMIG_v3.4.csv, unchanged, plus Named_In: the Statement_IDs that name the variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>READING</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Read with keep_default_na=False (pandas) or the equivalent, so that no cell is read as missing.</t>
         </is>
@@ -871,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1679,12 +1707,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>IS-A2</t>
+          <t>MI-A2</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>facet</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1694,7 +1722,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
+          <t>6.3.5.8 Microscopic Findings (MI); MI – Assumptions</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1704,36 +1732,36 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>MITESTCD; MITSTDTL</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>The IS domain also holds assessments that describe whether an allergen, microorganism, or endogenous molecule provoked/caused/induced an immune response in a subject, such as a subject's antibody reaction (autoantibodies) against auto/self-antigens for autoimmune studies or antibody production in response to allergens in allergy trials. Expected outputs can be positive or negative, present or absent for the antibody of interest, as well as quantification of the antibody. Assessments pertaining to antibodies produced in response to microbial infection will also be represented in the IS domain.</t>
+          <t>When biomarker results are represented in MI, MITESTCD reflects the biomarker of interest (e.g., "BRCA1", "HER2", "TTF1"), and MITSTDTL further qualifies the record. MITSTDTL is used to represent details descriptive of staining results (e.g., "H SCORE TOTAL SCORE", "STAINING INTENSITY", "PERCENT POSITIVE CELL").</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IS-A5</t>
+          <t>MITSTDTL-Notes</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>facet</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1743,46 +1771,34 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>An exception is made to the class of antigen/antibody (Ag/Ab) combination assays. Microbial antigen/antibody (Ag/Ab) combination tests should be represented in the Microbiology Specimen (MB) domain. An example is fourth-generation HIV Ag/Ab combination tests, which are commonly seen as HIV identification or detection assays rather than tests that provide additional details on and characterization of a subject’s immunological responses. The outputs of these assays can be expected as reactive, non-reactive, or indeterminate. Whereas some tests generate separate outputs for antigen and antibody, others just indicate “reactive” when either or both are detected. Output is generally based on relative light units, where a result of "reactive" typically requires the signal to cutoff ratio to be greater than 1.</t>
+          <t>Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>IS-A6</t>
+          <t>GFTSTDTL-Notes</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>facet</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1792,46 +1808,38 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>GFTESTCD; GFTEST</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
+      <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Measurements of cytokines, chemokines, and complement proteins should be represented in the Laboratory Test Results (LB) domain.</t>
+          <t>Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GF-A1</t>
+          <t>GFANMETH-Notes</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>facet</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1841,19 +1849,11 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
           <t>GF</t>
@@ -1861,26 +1861,22 @@
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>GF</t>
-        </is>
-      </c>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>The Genomics Findings domain is used to represent findings related to the structure, function, evolution, mapping, and editing of subject and non-host organism genomic material of interest. This domain includes but is not limited to assessments and results for genetic variation and transcription, and summary measures derived from these assessments. The GF domain is used for findings from characteristics assessed from nucleic acids and may include subsequent inferences and/or predictions about related proteins/amino acids. However, direct assessments of proteins (e.g., assessments of amino acids) are out of scope for this domain.</t>
+          <t>The method of secondary processing performed by the dry lab to yield the result reported in the dataset.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>GF-A2</t>
+          <t>ISMSCBCE-Notes</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>routing</t>
+          <t>facet</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1890,37 +1886,33 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>ISTEST; ISMSCBCE</t>
+        </is>
+      </c>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Regarding genetic testing on non-host organisms (including but not limited to bacteria, viruses, and parasites), the following additional assumptions apply:</t>
+          <t>Text description of the entity secreted by the cells represented in ISTEST. The combination of ISTEST and ISMSCBCE should describe the entity or the analyte being measured, without the need for additional variables.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>GF-A2a</t>
+          <t>IS-A2</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1935,37 +1927,41 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Tests that give genetic results (e.g., expressed in terms of genetic variation, specific sequence information) on non-host organisms that have been identified in subject samples should be represented in GF. To distinguish these findings from subject genetic data, the variable NHOID must be populated to identify the non-host organism as the focus of the record (see Section 9.2, Non-host Organism Identifiers, assumption 2 for more information).</t>
+          <t>The IS domain also holds assessments that describe whether an allergen, microorganism, or endogenous molecule provoked/caused/induced an immune response in a subject, such as a subject's antibody reaction (autoantibodies) against auto/self-antigens for autoimmune studies or antibody production in response to allergens in allergy trials. Expected outputs can be positive or negative, present or absent for the antibody of interest, as well as quantification of the antibody. Assessments pertaining to antibodies produced in response to microbial infection will also be represented in the IS domain.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>GF-A2b</t>
+          <t>IS-A5</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1980,22 +1976,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2b</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
@@ -2007,14 +2003,14 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>If the purpose of the test is to detect or determine the identity of a viable, non-host organism or infectious agent in a subject sample, data should be represented in the Microbiology Specimen (MB) domain.</t>
+          <t>An exception is made to the class of antigen/antibody (Ag/Ab) combination assays. Microbial antigen/antibody (Ag/Ab) combination tests should be represented in the Microbiology Specimen (MB) domain. An example is fourth-generation HIV Ag/Ab combination tests, which are commonly seen as HIV identification or detection assays rather than tests that provide additional details on and characterization of a subject’s immunological responses. The outputs of these assays can be expected as reactive, non-reactive, or indeterminate. Whereas some tests generate separate outputs for antigen and antibody, others just indicate “reactive” when either or both are detected. Output is generally based on relative light units, where a result of "reactive" typically requires the signal to cutoff ratio to be greater than 1.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>GF-A2c</t>
+          <t>IS-A6</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2029,41 +2025,41 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2c</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Tests that are used to determine the resistance/susceptibility of a non-host organism to a drug on a genetic basis should be represented in the Microbiology Susceptibility (MS) domain.</t>
+          <t>Measurements of cytokines, chemokines, and complement proteins should be represented in the Laboratory Test Results (LB) domain.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>GF-A2d</t>
+          <t>GF-A1</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2083,12 +2079,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2100,19 +2096,19 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>If the test provides both genetic data and susceptibility/resistance data, genetic data should be represented in GF and the susceptibility/resistance data should be represented in the MS domain (See Section 6.3.5.7.2, Microbiology Susceptibility, assumption 1b for more information).</t>
+          <t>The Genomics Findings domain is used to represent findings related to the structure, function, evolution, mapping, and editing of subject and non-host organism genomic material of interest. This domain includes but is not limited to assessments and results for genetic variation and transcription, and summary measures derived from these assessments. The GF domain is used for findings from characteristics assessed from nucleic acids and may include subsequent inferences and/or predictions about related proteins/amino acids. However, direct assessments of proteins (e.g., assessments of amino acids) are out of scope for this domain.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>GF-A8</t>
+          <t>GF-A2</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2132,12 +2128,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2145,23 +2141,19 @@
           <t>GF</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>GFMETHOD</t>
-        </is>
-      </c>
+      <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.</t>
+          <t>Regarding genetic testing on non-host organisms (including but not limited to bacteria, viruses, and parasites), the following additional assumptions apply:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>MB-A1</t>
+          <t>GF-A2a</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2176,22 +2168,22 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2a</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
@@ -2199,14 +2191,14 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Representation of findings in the Microbiology Specimen domain should be handled as follows:</t>
+          <t>Tests that give genetic results (e.g., expressed in terms of genetic variation, specific sequence information) on non-host organisms that have been identified in subject samples should be represented in GF. To distinguish these findings from subject genetic data, the variable NHOID must be populated to identify the non-host organism as the focus of the record (see Section 9.2, Non-host Organism Identifiers, assumption 2 for more information).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>MB-A1a</t>
+          <t>GF-A2b</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2221,41 +2213,41 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>2b</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>MBTEST; MBTSTDTL</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>In cases of tests that target an organism, group of organisms, or antigen for identification, MBTEST equals the name of the organism/antigen targeted by the identification assay, and i. MBTSTDTL should be “DETECTION”. ii. The result should generally be "PRESENT"/"ABSENT", "POSITIVE"/"NEGATIVE", or "INDETERMINATE". However, there may be cases where a test differentiates between 2 or more similar organisms, in which case it would be appropriate for the result to be the name of the organism detected. For example, a test may look for influenza A or influenza B antigen. In this case, MBTEST would be "Influenza A/B Antigen"; the result could be "INFLUENZA A ANTIGEN", "INFLUENZA B ANTIGEN", or "INFLUENZA A/B ANTIGEN".</t>
+          <t>If the purpose of the test is to detect or determine the identity of a viable, non-host organism or infectious agent in a subject sample, data should be represented in the Microbiology Specimen (MB) domain.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>MB-A1b</t>
+          <t>GF-A2c</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2270,41 +2262,41 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1b</t>
+          <t>2c</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>MBTESTCD; MBTEST; MBORRES</t>
-        </is>
-      </c>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>For non-targeted identification of organisms (i.e., tests that have the ability to identify a range of organisms without specifically targeting any), the value for MBTESTCD/MBTEST should be "MCORGIDN"/"Microbial Organism Identification", and the result should be the name of the organism or group of organisms found to be present (e.g., "INFLUENZA A VIRUS SUBTYPE H1N1"; "CLONORCHIS SINENSIS"). In this scenario MBORRES is populated with values from the Microorganism Codelist (C85491).</t>
+          <t>Tests that are used to determine the resistance/susceptibility of a non-host organism to a drug on a genetic basis should be represented in the Microbiology Susceptibility (MS) domain.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PCTESTCD-Notes</t>
+          <t>GF-A2d</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2319,33 +2311,41 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Variable table, CDISC Notes</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>PCTESTCD</t>
-        </is>
-      </c>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
+          <t>If the test provides both genetic data and susceptibility/resistance data, genetic data should be represented in GF and the susceptibility/resistance data should be represented in the MS domain (See Section 6.3.5.7.2, Microbiology Susceptibility, assumption 1b for more information).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PCTEST-Notes</t>
+          <t>GF-A8</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2360,33 +2360,41 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Variable table, CDISC Notes</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>PCTEST</t>
+          <t>GFMETHOD</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
+          <t>GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>RS-DR-A1</t>
+          <t>MB-A1</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2401,7 +2409,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2411,29 +2419,605 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>RSCAT</t>
-        </is>
-      </c>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
+          <t>Representation of findings in the Microbiology Specimen domain should be handled as follows:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>MB-A1a</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>MBTEST; MBTSTDTL</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>In cases of tests that target an organism, group of organisms, or antigen for identification, MBTEST equals the name of the organism/antigen targeted by the identification assay, and i. MBTSTDTL should be “DETECTION”. ii. The result should generally be "PRESENT"/"ABSENT", "POSITIVE"/"NEGATIVE", or "INDETERMINATE". However, there may be cases where a test differentiates between 2 or more similar organisms, in which case it would be appropriate for the result to be the name of the organism detected. For example, a test may look for influenza A or influenza B antigen. In this case, MBTEST would be "Influenza A/B Antigen"; the result could be "INFLUENZA A ANTIGEN", "INFLUENZA B ANTIGEN", or "INFLUENZA A/B ANTIGEN".</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>MB-A1b</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>MBTESTCD; MBTEST; MBORRES</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>For non-targeted identification of organisms (i.e., tests that have the ability to identify a range of organisms without specifically targeting any), the value for MBTESTCD/MBTEST should be "MCORGIDN"/"Microbial Organism Identification", and the result should be the name of the organism or group of organisms found to be present (e.g., "INFLUENZA A VIRUS SUBTYPE H1N1"; "CLONORCHIS SINENSIS"). In this scenario MBORRES is populated with values from the Microorganism Codelist (C85491).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>PCTESTCD-Notes</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>PCTESTCD</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>PCTEST-Notes</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>PCTEST</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A1</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
           <t>RSCAT is used to group a set of assessments based on a disease response criterion (published or protocol-defined). One of the codelists for RSCAT is ONCRSCAT. The ONCRSCAT codelist contains controlled terminology for oncology disease response assessments.</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A6b</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>6b</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>If the criteria used to determine the response is unknown or not collected, this is represented as RSCAT = "UNSPECIFIED".</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A9</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>RSTEST; RSCAT</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Disease recurrence can be represented in the RS domain using RSTEST = "Disease Recurrence Indicator" to indicate that there was an assessment of whether there was disease recurrence. The RSCAT = "PROTOCOL DEFINED RESPONSE CRITERIA" can be used to indicate that the response assessment of disease recurrence was based on protocol-specified criteria rather than published response criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>RS-CC-A2</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.3.2 Clinical Classifications Use Case; RS – Clinical Classifications Use Case Assumptions</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>RSCAT is used to group a set of assessments based on a clinical classification. One of the codelists for RSCAT is CCCAT. The CCCAT codelist contains CDISC Controlled Terminology for clinical classifications instruments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A7</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>RSEVALID; RSEVAL</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>The evaluator identifier variable (RSEVALID) can be used in conjunction with RSEVAL to provide additional detail of who is providing the assessment. For example, RSEVAL = "INDEPENDENT ASSESSOR" and RSEVALID = "RADIOLOGIST 1" may further qualify the RSEVALID variable. RSEVALID may be subject to controlled terminology but may also represent free text values depending on the use case. When used with disease response data, RSEVALID is subject to MEDEVAL controlled terminology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>QS-A8</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>6.3.9.2 Questionnaires (QS); QS – Assumptions</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>--EVAL and --EVALID must not be used to model QRS data in SDTM. These variables have had various interpretations on QRS CRFs and were used to represent a multitude of evaluator information about QRS instruments. This has made it more difficult for users of SDTM QRS data to interpret this data and more difficult to pool data for analyses. If needed, supplemental qualifiers may be used to represent this data. Updated information on a proposed solution to this issue will be posted on the CDISC QRS webpage (https://www.cdisc.org/standards/foundational/qrs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TR-A1</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>6.3.12.2 Tumor/Lesion Results (TR); TR – Assumptions</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKID</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>TR; TU</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKID is used to relate records in the TR domain to an identification record in TU domain. The organization of data across the TU and TR domains requires a RELREC relationship to link the related data rows. A dataset-to-dataset link would be the most appropriate linking mechanism. Utilizing 1 of the existing ID variables is not possible, because --GRPID, --REFID, and --SPID may be used for other purposes, per the SDTM. The --LNKID variable is used for values that support a RELREC dataset-to-dataset relationship and to provide a unique code for each identified tumor/lesion/location of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TR-A2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>6.3.12.2 Tumor/Lesion Results (TR); TR – Assumptions</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKGRP</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>TR; RS</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKGRP is used to relate records in the TR domain to a response assessment record in the RS domain. The organization of data across the TR and RS domains requires a RELREC relationship to link the related data rows. A dataset-to-dataset link would be the most appropriate linking mechanism. Utilizing 1 of the existing ID variables is not possible because --GRPID, --REFID, and --SPID may be used for other purposes, per the SDTM. The --LNKGRP variable is used for values that support a RELREC dataset-to-dataset relationship and to provide a unique code for each response and associated tumor/lesion measurements/assessments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2444,7 +3028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2461,7 +3045,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="120" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2602,7 +3186,7 @@
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>GF-A5a</t>
+          <t>GF-A5a; GFTSTDTL-Notes</t>
         </is>
       </c>
     </row>
@@ -2667,7 +3251,7 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>GF-A5a</t>
+          <t>GF-A5a; GFTSTDTL-Notes</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3442,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>ISBDAGNT-Notes</t>
+          <t>ISBDAGNT-Notes; ISMSCBCE-Notes</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3584,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3010,17 +3594,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>LBTEST</t>
+          <t>ISMSCBCE</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Lab Test or Examination Name</t>
+          <t>Molecule Secreted by Cells</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3028,32 +3612,28 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>C67154</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Variable Qualifier</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Verbatim name of the test or examination used to obtain the measurement or finding. Note: Any test normally performed by a clinical laboratory is considered a lab test. The value in LBTEST cannot be longer than 40 characters. Examples: "Alanine Aminotransferase", "Lactate Dehydrogenase".</t>
+          <t>Text description of the entity secreted by the cells represented in ISTEST. The combination of ISTEST and ISMSCBCE should describe the entity or the analyte being measured, without the need for additional variables.</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>LB-A8</t>
+          <t>ISMSCBCE-Notes</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3645,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3080,12 +3660,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>LBTSTCND</t>
+          <t>LBTEST</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Test Condition</t>
+          <t>Lab Test or Examination Name</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3095,7 +3675,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>C181175</t>
+          <t>C67154</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
@@ -3103,17 +3683,17 @@
       <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Variable Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Identifies any planned condition imposed by the assay system on the specimen at the time the test is performed.</t>
+          <t>Verbatim name of the test or examination used to obtain the measurement or finding. Note: Any test normally performed by a clinical laboratory is considered a lab test. The value in LBTEST cannot be longer than 40 characters. Examples: "Alanine Aminotransferase", "Lactate Dehydrogenase".</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Perm</t>
+          <t>Req</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -3130,7 +3710,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3145,12 +3725,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>LBBDAGNT</t>
+          <t>LBTSTCND</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Binding Agent</t>
+          <t>Test Condition</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -3158,7 +3738,11 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>C181175</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr"/>
@@ -3169,7 +3753,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>The textual description of the agent that is binding to the entity in the LBTEST variable. The LBBDAGNT variable is used to indicate that there is a binding relationship between the entities in the LBTEST and LBBDAGNT variables, regardless of direction. \n LBBDAGNT is not a method qualifier. It should only be used when the actual interest of the measurement is the binding interaction between the 2 entities in LBTEST and LBBDAGNT. In other words, the combination of LBTEST and LBBDAGNT should describe the thing, the entity, or the analyte being measured, without the need for additional variables. \n The binding agent may be (but is not limited to) a test article, a portion of the test article, a related compound, or an endogenous molecule.</t>
+          <t>Identifies any planned condition imposed by the assay system on the specimen at the time the test is performed.</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -3191,7 +3775,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3206,12 +3790,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>LBTSTOPO</t>
+          <t>LBBDAGNT</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Test Operational Objective</t>
+          <t>Binding Agent</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3219,11 +3803,7 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>C181170</t>
-        </is>
-      </c>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
@@ -3234,7 +3814,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Text description of the high-level purpose of the test at the operational level.</t>
+          <t>The textual description of the agent that is binding to the entity in the LBTEST variable. The LBBDAGNT variable is used to indicate that there is a binding relationship between the entities in the LBTEST and LBBDAGNT variables, regardless of direction. \n LBBDAGNT is not a method qualifier. It should only be used when the actual interest of the measurement is the binding interaction between the 2 entities in LBTEST and LBBDAGNT. In other words, the combination of LBTEST and LBBDAGNT should describe the thing, the entity, or the analyte being measured, without the need for additional variables. \n The binding agent may be (but is not limited to) a test article, a portion of the test article, a related compound, or an endogenous molecule.</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -3256,7 +3836,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -3271,12 +3851,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>LBORRESU</t>
+          <t>LBTSTOPO</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Original Units</t>
+          <t>Test Operational Objective</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3286,7 +3866,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C181170</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
@@ -3299,12 +3879,12 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Original units in which the data were collected. The unit for LBORRES. Example: "g/L".</t>
+          <t>Text description of the high-level purpose of the test at the operational level.</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -3321,7 +3901,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3336,12 +3916,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>LBRESSCL</t>
+          <t>LBORRESU</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Result Scale</t>
+          <t>Original Units</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3351,7 +3931,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>C177910</t>
+          <t>C71620</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
@@ -3359,17 +3939,17 @@
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Variable Qualifier</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Classifies the scale of the original result value; for example, whether the result is ordinal, nominal, quantitative, or narrative.</t>
+          <t>Original units in which the data were collected. The unit for LBORRES. Example: "g/L".</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Perm</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -3386,7 +3966,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3401,12 +3981,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>LBRESTYP</t>
+          <t>LBRESSCL</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Result Type</t>
+          <t>Result Scale</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3416,7 +3996,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>C179588</t>
+          <t>C177910</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
@@ -3429,7 +4009,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Classifies the kind of result (i.e., property type) originally reported for the test. Examples include substance concentration, proportion, mass rate, and arbitrary concentration.</t>
+          <t>Classifies the scale of the original result value; for example, whether the result is ordinal, nominal, quantitative, or narrative.</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -3451,7 +4031,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3466,12 +4046,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>LBCOLSRT</t>
+          <t>LBRESTYP</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Collected Summary Result Type</t>
+          <t>Result Type</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3481,7 +4061,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>C177908</t>
+          <t>C179588</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
@@ -3494,7 +4074,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Used to indicate the type of collected summary result. This includes source summary results collected on a CRF or provided by an external vendor (e.g., central lab). If the summary result is derived by the sponsor using individual source data records from SDTM, the derived summary result is represented in ADaM. If the summary result is produced and reported by the lab, the collected summary result is represented in SDTM.</t>
+          <t>Classifies the kind of result (i.e., property type) originally reported for the test. Examples include substance concentration, proportion, mass rate, and arbitrary concentration.</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -3516,7 +4096,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -3531,12 +4111,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>LBLLOD</t>
+          <t>LBCOLSRT</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Lower Limit of Detection</t>
+          <t>Collected Summary Result Type</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3544,18 +4124,22 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>C177908</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Variable Qualifier</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>The lowest threshold (as originally received or collected) for reliably detecting the presence or absence of substance measured by a specific test. The value for the field will be as described in documentation from the instrument or lab vendor.</t>
+          <t>Used to indicate the type of collected summary result. This includes source summary results collected on a CRF or provided by an external vendor (e.g., central lab). If the summary result is derived by the sponsor using individual source data records from SDTM, the derived summary result is represented in ADaM. If the summary result is produced and reported by the lab, the collected summary result is represented in SDTM.</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -3577,7 +4161,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3592,12 +4176,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>LBLOINC</t>
+          <t>LBLLOD</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>LOINC Code</t>
+          <t>Lower Limit of Detection</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3607,20 +4191,16 @@
       </c>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>LOINC</t>
-        </is>
-      </c>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Variable Qualifier</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Code for the lab test from the LOINC code system. The sponsor is expected to provide the dictionary name and version used to map the terms utilizing the Define-XML external codelist attributes.</t>
+          <t>The lowest threshold (as originally received or collected) for reliably detecting the presence or absence of substance measured by a specific test. The value for the field will be as described in documentation from the instrument or lab vendor.</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -3642,7 +4222,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3657,12 +4237,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>LBSPEC</t>
+          <t>LBLOINC</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>LOINC Code</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -3670,22 +4250,22 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>C78734</t>
-        </is>
-      </c>
+      <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LOINC</t>
+        </is>
+      </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Record Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Defines the type of specimen used for a measurement. Examples: "SERUM", "PLASMA", "URINE".</t>
+          <t>Code for the lab test from the LOINC code system. The sponsor is expected to provide the dictionary name and version used to map the terms utilizing the Define-XML external codelist attributes.</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3707,7 +4287,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3722,12 +4302,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>LBMETHOD</t>
+          <t>LBSPEC</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Method of Test or Examination</t>
+          <t>Specimen Type</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -3737,7 +4317,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>C85492</t>
+          <t>C78734</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
@@ -3750,7 +4330,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Method of the test or examination. Examples: "EIA" (enzyme immunoassay), "ELECTROPHORESIS", "DIPSTICK".</t>
+          <t>Defines the type of specimen used for a measurement. Examples: "SERUM", "PLASMA", "URINE".</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -3772,7 +4352,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3787,12 +4367,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>LBANMETH</t>
+          <t>LBMETHOD</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Analysis Method</t>
+          <t>Method of Test or Examination</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -3802,7 +4382,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>C160922</t>
+          <t>C85492</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
@@ -3815,7 +4395,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Analysis method applied to obtain a summarized result. Analysis method describes the method of secondary processing applied to a complex observation result (e.g., a calculation used to measure eGFR).</t>
+          <t>Method of the test or examination. Examples: "EIA" (enzyme immunoassay), "ELECTROPHORESIS", "DIPSTICK".</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -3837,7 +4417,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3852,12 +4432,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>LBFAST</t>
+          <t>LBANMETH</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Fasting Status</t>
+          <t>Analysis Method</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3867,7 +4447,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>C66742</t>
+          <t>C160922</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr"/>
@@ -3880,7 +4460,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Indicator used to identify fasting status. Examples: "Y", "N".</t>
+          <t>Analysis method applied to obtain a summarized result. Analysis method describes the method of secondary processing applied to a complex observation result (e.g., a calculation used to measure eGFR).</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -3902,7 +4482,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3917,12 +4497,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>LBTPT</t>
+          <t>LBFAST</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Planned Time Point Name</t>
+          <t>Fasting Status</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3930,18 +4510,22 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Timing</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Text description of time when specimen should be taken. This may be represented as an elapsed time relative to a fixed reference point, such as time of last dose. See LBTPTNUM and LBTPTREF. Examples: "Start", "5 min post".</t>
+          <t>Indicator used to identify fasting status. Examples: "Y", "N".</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -3963,7 +4547,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3978,12 +4562,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>LBPTFL</t>
+          <t>LBTPT</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Point in Time Flag</t>
+          <t>Planned Time Point Name</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -3991,11 +4575,7 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>C66742</t>
-        </is>
-      </c>
+      <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
@@ -4006,7 +4586,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>An indication that the specimen was collected at a single point in time. The value is "Y" or null. The intent of this variable in the LB domain is to aid mapping to LOINC codes in the dataset, when LOINC part "Time Aspect" = "Pt".</t>
+          <t>Text description of time when specimen should be taken. This may be represented as an elapsed time relative to a fixed reference point, such as time of last dose. See LBTPTNUM and LBTPTREF. Examples: "Start", "5 min post".</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -4028,7 +4608,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4043,12 +4623,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>LBPDUR</t>
+          <t>LBPTFL</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Planned Duration</t>
+          <t>Point in Time Flag</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -4056,13 +4636,13 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>ISO 8601 duration</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="inlineStr">
         <is>
@@ -4071,7 +4651,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Planned duration of specimen collection. If LBPTFL is "Y" then LBPDUR is null.</t>
+          <t>An indication that the specimen was collected at a single point in time. The value is "Y" or null. The intent of this variable in the LB domain is to aid mapping to LOINC codes in the dataset, when LOINC part "Time Aspect" = "Pt".</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -4093,7 +4673,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -4103,17 +4683,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>MBGRPID</t>
+          <t>LBPDUR</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Group ID</t>
+          <t>Planned Duration</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -4123,16 +4703,20 @@
       </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>ISO 8601 duration</t>
+        </is>
+      </c>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Timing</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Optional group identifier, used to link together a block of related records within a subject in a domain.</t>
+          <t>Planned duration of specimen collection. If LBPTFL is "Y" then LBPDUR is null.</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -4142,7 +4726,7 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>MB-A1c</t>
+          <t>LB-A8</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4738,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4169,12 +4753,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>MBTESTCD</t>
+          <t>MBGRPID</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Microbiology Test or Finding Short Name</t>
+          <t>Group ID</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4182,32 +4766,28 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>C120527</t>
-        </is>
-      </c>
+      <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Short name of the measurement, test, or finding described in MBTEST. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in MBTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). MBTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "MCORGIDN" for Microbial Organism Identification "GMNCOC" for Gram Negative Cocci.</t>
+          <t>Optional group identifier, used to link together a block of related records within a subject in a domain.</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>MB-A1c; MBTSTDTL-Notes; MB-A1b</t>
+          <t>MB-A1c</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4799,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -4234,12 +4814,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>MBTEST</t>
+          <t>MBTESTCD</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Microbiology Test or Finding Name</t>
+          <t>Microbiology Test or Finding Short Name</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -4249,7 +4829,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>C120528</t>
+          <t>C120527</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
@@ -4257,12 +4837,12 @@
       <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Verbatim name of the test or examination used to obtain the measurement or finding. The value in MBTEST cannot be longer than 40 characters. Examples: "Microbial Organism Identification", "Gram Negative Cocci", "HIV-1 RNA".</t>
+          <t>Short name of the measurement, test, or finding described in MBTEST. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in MBTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). MBTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "MCORGIDN" for Microbial Organism Identification "GMNCOC" for Gram Negative Cocci.</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -4272,7 +4852,7 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>MB-A1c; MBTSTDTL-Notes; MB-A1a; MB-A1b</t>
+          <t>MB-A1c; MBTSTDTL-Notes; MB-A1b</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4864,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4299,12 +4879,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>MBTSTDTL</t>
+          <t>MBTEST</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Measurement, Test or Examination Detail</t>
+          <t>Microbiology Test or Finding Name</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -4314,7 +4894,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>C174225</t>
+          <t>C120528</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
@@ -4322,22 +4902,22 @@
       <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Variable Qualifier</t>
+          <t>Synonym Qualifier</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Further description of MBTESTCD and MBTEST. Example: "VIRAL LOAD" when MBTESTCD represents viral genetic material, such as "HCRNA", "QUANTIFICATION" when MBTESTCD represents any organism being quantified.</t>
+          <t>Verbatim name of the test or examination used to obtain the measurement or finding. The value in MBTEST cannot be longer than 40 characters. Examples: "Microbial Organism Identification", "Gram Negative Cocci", "HIV-1 RNA".</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Perm</t>
+          <t>Req</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>MB-A1c; MB-A1a</t>
+          <t>MB-A1c; MBTSTDTL-Notes; MB-A1a; MB-A1b</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4929,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -4364,12 +4944,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>MBORRES</t>
+          <t>MBTSTDTL</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Result or Finding in Original Units</t>
+          <t>Measurement, Test or Examination Detail</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -4377,28 +4957,32 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>C174225</t>
+        </is>
+      </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Result Qualifier</t>
+          <t>Variable Qualifier</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Result of the microbiology measurement or finding as originally received or collected. Examples for "GRAM STAIN" findings: "+3 MODERATE", "+2 FEW", "&lt;10". Examples for "CULTURE PLATE" findings: "KLEBSIELLA PNEUMONIAE", "STREPTOCOCCUS PNEUMONIAE".</t>
+          <t>Further description of MBTESTCD and MBTEST. Example: "VIRAL LOAD" when MBTESTCD represents viral genetic material, such as "HCRNA", "QUANTIFICATION" when MBTESTCD represents any organism being quantified.</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>MB-A1b</t>
+          <t>MB-A1c; MB-A1a</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4994,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4420,17 +5004,17 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>MKTESTCD</t>
+          <t>MBORRES</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Short Name of Musculoskeletal Test</t>
+          <t>Result or Finding in Original Units</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -4438,32 +5022,28 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>C127269</t>
-        </is>
-      </c>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Result Qualifier</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Short character value for MKTEST used as a column name when converting a dataset from a vertical format to a horizontal format. The value in MKTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). MKTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "TNDRIND", "SWLLIND", "SGJSNSCR".</t>
+          <t>Result of the microbiology measurement or finding as originally received or collected. Examples for "GRAM STAIN" findings: "+3 MODERATE", "+2 FEW", "&lt;10". Examples for "CULTURE PLATE" findings: "KLEBSIELLA PNEUMONIAE", "STREPTOCOCCUS PNEUMONIAE".</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>4.1.9-4</t>
+          <t>MB-A1b</t>
         </is>
       </c>
     </row>
@@ -4475,7 +5055,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -4485,17 +5065,17 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>MKTEST</t>
+          <t>MITESTCD</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Name of Musculoskeletal Test</t>
+          <t>Microscopic Examination Short Name</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -4505,7 +5085,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>C127270</t>
+          <t>C132263</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
@@ -4513,12 +5093,12 @@
       <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Long name For MKTESTCD. Examples: "Tenderness Indicator", "Swollen Indicator", "Sharp/Genant JSN Score".</t>
+          <t>Short name of the measurement, test, or examination described in MITEST. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in MITESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). MITESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "HER2", "BRCA1", "TTF1".</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -4528,7 +5108,7 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>4.1.9-2</t>
+          <t>MI-A2</t>
         </is>
       </c>
     </row>
@@ -4540,7 +5120,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4550,17 +5130,17 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>PCTESTCD</t>
+          <t>MITSTDTL</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Pharmacokinetic Test Short Name</t>
+          <t>Microscopic Examination Detail</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4568,28 +5148,32 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>C125922</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Record Qualifier</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
+          <t>Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>PCTESTCD-Notes</t>
+          <t>MI-A2</t>
         </is>
       </c>
     </row>
@@ -4601,7 +5185,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -4611,17 +5195,17 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>PCTEST</t>
+          <t>MKTESTCD</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Pharmacokinetic Test Name</t>
+          <t>Short Name of Musculoskeletal Test</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4629,18 +5213,22 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>C127269</t>
+        </is>
+      </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Synonym Qualifier</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
+          <t>Short character value for MKTEST used as a column name when converting a dataset from a vertical format to a horizontal format. The value in MKTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). MKTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "TNDRIND", "SWLLIND", "SGJSNSCR".</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -4650,7 +5238,7 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>PCTEST-Notes</t>
+          <t>4.1.9-4</t>
         </is>
       </c>
     </row>
@@ -4662,7 +5250,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -4672,17 +5260,17 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>RSCAT</t>
+          <t>MKTEST</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Category for Assessment</t>
+          <t>Name of Musculoskeletal Test</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4692,7 +5280,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>C124298; C118971</t>
+          <t>C127270</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
@@ -4700,27 +5288,531 @@
       <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="5" t="inlineStr">
         <is>
+          <t>Synonym Qualifier</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Long name For MKTESTCD. Examples: "Tenderness Indicator", "Swollen Indicator", "Sharp/Genant JSN Score".</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>Req</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>4.1.9-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>PCTESTCD</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic Test Short Name</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>Req</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>PCTESTCD-Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>PCTEST</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic Test Name</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Synonym Qualifier</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>Req</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>PCTEST-Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>RSTEST</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Assessment Name</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>C96781</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Synonym Qualifier</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Verbatim name of the response assessment. The value in RSTEST cannot be longer than 40 characters. \n There are separate codelists used for RSTEST where the choice depends on the value of RSCAT. Codelist "ONCRTS" is used for oncology response criteria (when RSCAT is a term in codelist "ONCRSCAT"). Examples: "Target Response", "Non-target Response", "Overall Response", "Symptomatic Deterioration". For Clinical Classifications (when RSCAT is a term in codelist "CCCAT"), QRS Naming Rules apply. These instruments have individual dedicated terminology codelists.</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>Req</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Category for Assessment</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>C124298; C118971</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
           <t>Grouping Qualifier</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Used to define a category of related records across subjects. Examples: "RECIST 1.1", "CHILD-PUGH CLASSIFICATION". There are separate codelists used for RSCAT where the choice depends on whether the related records are about an oncology response criterion or another clinical classification. \n RSCAT is required for clinical classifications other than oncology response criteria.</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Exp</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>RS-DR-A1</t>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A1; RS-DR-A6b; RS-DR-A9; RS-CC-A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>RSEVAL</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Evaluator</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>C78735</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Role of the person who provided the evaluation. Used only for results that are subjective (e.g., assigned by a person or a group). Examples: "ADJUDICATION COMMITTEE", "INDEPENDENT ASSESSOR", "RADIOLOGIST". \n RSEVAL is expected for oncology response criteria. It can be left null when the investigator provides the complete set of data in the domain. However, the column should contain no null values when data from one or more independent assessors is included, meaning that the rows attributed to the investigator should contain a value of "INVESTIGATOR".</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>RSEVALID</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Evaluator Identifier</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>C96777</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Variable Qualifier</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Used to distinguish multiple evaluators with the same role recorded in RSEVAL. Examples: "RADIOLOGIST1", "RADIOLOGIST2". See assumptions in Section 6.3.9.3.1, Disease Response Use Case.</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>RS-DR-A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKID</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Link ID</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Identifier used to link the assessment result records to the individual tumor/lesion identification record in TU domain.</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>TR-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKGRP</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Link Group</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Used to group and link all of the measurement/assessment records used in the assessment of the response record in the RS domain.</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Perm</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>TR-A2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4818,7 +5910,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31 14:39</t>
+          <t>2026-10-31 22:14</t>
         </is>
       </c>
     </row>
@@ -4842,7 +5934,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -4866,7 +5958,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6f947576c1b4d890a5cb2525563b91bd829d5355162bea16a7bd83b150f71edd</t>
+          <t>1b72ffa81f9f4bf123a5f0e5e182a6f8cd5313f5e70bd8e9c0ab2c97ae760da7</t>
         </is>
       </c>
     </row>
@@ -4878,7 +5970,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -4902,7 +5994,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>8ca3d21a811eaec137a68d7ee38cfd7bf591b62f5cc7207e838da0b92348567f</t>
+          <t>8fb84633742541ffbe27ff176ec559bbaf639f35af00919682c5c129d917f9e3</t>
         </is>
       </c>
     </row>

--- a/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Statements'!$A$1:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Statements'!$A$1:$K$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Variables'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>44 statements: 21 selected as facet, 19 as routing, 4 as record. 42 variables.</t>
+          <t>45 statements: 21 selected as facet, 20 as routing, 4 as record. 42 variables.</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-31 22:14</t>
+          <t>Generated: 2026-11-01 09:42</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1961,7 +1961,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>IS-A5</t>
+          <t>IS-A4</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1998,19 +1998,19 @@
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>An exception is made to the class of antigen/antibody (Ag/Ab) combination assays. Microbial antigen/antibody (Ag/Ab) combination tests should be represented in the Microbiology Specimen (MB) domain. An example is fourth-generation HIV Ag/Ab combination tests, which are commonly seen as HIV identification or detection assays rather than tests that provide additional details on and characterization of a subject’s immunological responses. The outputs of these assays can be expected as reactive, non-reactive, or indeterminate. Whereas some tests generate separate outputs for antigen and antibody, others just indicate “reactive” when either or both are detected. Output is generally based on relative light units, where a result of "reactive" typically requires the signal to cutoff ratio to be greater than 1.</t>
+          <t>Certain types of cellular immune responses will also be modeled in IS using non-flow cytometry techniques (see example 6). Flow cytometry data should be modeled in the Cell Phenotype Findings (CP) domain, section 6.3.5.3.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IS-A6</t>
+          <t>IS-A5</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2047,19 +2047,19 @@
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Measurements of cytokines, chemokines, and complement proteins should be represented in the Laboratory Test Results (LB) domain.</t>
+          <t>An exception is made to the class of antigen/antibody (Ag/Ab) combination assays. Microbial antigen/antibody (Ag/Ab) combination tests should be represented in the Microbiology Specimen (MB) domain. An example is fourth-generation HIV Ag/Ab combination tests, which are commonly seen as HIV identification or detection assays rather than tests that provide additional details on and characterization of a subject’s immunological responses. The outputs of these assays can be expected as reactive, non-reactive, or indeterminate. Whereas some tests generate separate outputs for antigen and antibody, others just indicate “reactive” when either or both are detected. Output is generally based on relative light units, where a result of "reactive" typically requires the signal to cutoff ratio to be greater than 1.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>GF-A1</t>
+          <t>IS-A6</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2074,41 +2074,41 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
+          <t>6.3.5.5 Immunogenicity Specimen Assessments (IS); IS – Assumptions</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>The Genomics Findings domain is used to represent findings related to the structure, function, evolution, mapping, and editing of subject and non-host organism genomic material of interest. This domain includes but is not limited to assessments and results for genetic variation and transcription, and summary measures derived from these assessments. The GF domain is used for findings from characteristics assessed from nucleic acids and may include subsequent inferences and/or predictions about related proteins/amino acids. However, direct assessments of proteins (e.g., assessments of amino acids) are out of scope for this domain.</t>
+          <t>Measurements of cytokines, chemokines, and complement proteins should be represented in the Laboratory Test Results (LB) domain.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>GF-A2</t>
+          <t>GF-A1</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2143,17 +2143,21 @@
       </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Regarding genetic testing on non-host organisms (including but not limited to bacteria, viruses, and parasites), the following additional assumptions apply:</t>
+          <t>The Genomics Findings domain is used to represent findings related to the structure, function, evolution, mapping, and editing of subject and non-host organism genomic material of interest. This domain includes but is not limited to assessments and results for genetic variation and transcription, and summary measures derived from these assessments. The GF domain is used for findings from characteristics assessed from nucleic acids and may include subsequent inferences and/or predictions about related proteins/amino acids. However, direct assessments of proteins (e.g., assessments of amino acids) are out of scope for this domain.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>GF-A2a</t>
+          <t>GF-A2</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2173,7 +2177,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2191,14 +2195,14 @@
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Tests that give genetic results (e.g., expressed in terms of genetic variation, specific sequence information) on non-host organisms that have been identified in subject samples should be represented in GF. To distinguish these findings from subject genetic data, the variable NHOID must be populated to identify the non-host organism as the focus of the record (see Section 9.2, Non-host Organism Identifiers, assumption 2 for more information).</t>
+          <t>Regarding genetic testing on non-host organisms (including but not limited to bacteria, viruses, and parasites), the following additional assumptions apply:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>GF-A2b</t>
+          <t>GF-A2a</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2218,7 +2222,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2b</t>
+          <t>2a</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2233,21 +2237,17 @@
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>If the purpose of the test is to detect or determine the identity of a viable, non-host organism or infectious agent in a subject sample, data should be represented in the Microbiology Specimen (MB) domain.</t>
+          <t>Tests that give genetic results (e.g., expressed in terms of genetic variation, specific sequence information) on non-host organisms that have been identified in subject samples should be represented in GF. To distinguish these findings from subject genetic data, the variable NHOID must be populated to identify the non-host organism as the focus of the record (see Section 9.2, Non-host Organism Identifiers, assumption 2 for more information).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>GF-A2c</t>
+          <t>GF-A2b</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2c</t>
+          <t>2b</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2284,19 +2284,19 @@
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Tests that are used to determine the resistance/susceptibility of a non-host organism to a drug on a genetic basis should be represented in the Microbiology Susceptibility (MS) domain.</t>
+          <t>If the purpose of the test is to detect or determine the identity of a viable, non-host organism or infectious agent in a subject sample, data should be represented in the Microbiology Specimen (MB) domain.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>GF-A2d</t>
+          <t>GF-A2c</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>2c</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2338,14 +2338,14 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>If the test provides both genetic data and susceptibility/resistance data, genetic data should be represented in GF and the susceptibility/resistance data should be represented in the MS domain (See Section 6.3.5.7.2, Microbiology Susceptibility, assumption 1b for more information).</t>
+          <t>Tests that are used to determine the resistance/susceptibility of a non-host organism to a drug on a genetic basis should be represented in the Microbiology Susceptibility (MS) domain.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>GF-A8</t>
+          <t>GF-A2d</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2378,23 +2378,23 @@
           <t>GF</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>GFMETHOD</t>
-        </is>
-      </c>
+      <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.</t>
+          <t>If the test provides both genetic data and susceptibility/resistance data, genetic data should be represented in GF and the susceptibility/resistance data should be represented in the MS domain (See Section 6.3.5.7.2, Microbiology Susceptibility, assumption 1b for more information).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MB-A1</t>
+          <t>GF-A8</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2409,37 +2409,41 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+          <t>6.3.5.4 Genomics Findings (GF); GF – Assumptions</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>GFMETHOD</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Representation of findings in the Microbiology Specimen domain should be handled as follows:</t>
+          <t>GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>MB-A1a</t>
+          <t>MB-A1</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2459,7 +2463,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>1a</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2472,23 +2476,19 @@
           <t>MB</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>MBTEST; MBTSTDTL</t>
-        </is>
-      </c>
+      <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>In cases of tests that target an organism, group of organisms, or antigen for identification, MBTEST equals the name of the organism/antigen targeted by the identification assay, and i. MBTSTDTL should be “DETECTION”. ii. The result should generally be "PRESENT"/"ABSENT", "POSITIVE"/"NEGATIVE", or "INDETERMINATE". However, there may be cases where a test differentiates between 2 or more similar organisms, in which case it would be appropriate for the result to be the name of the organism detected. For example, a test may look for influenza A or influenza B antigen. In this case, MBTEST would be "Influenza A/B Antigen"; the result could be "INFLUENZA A ANTIGEN", "INFLUENZA B ANTIGEN", or "INFLUENZA A/B ANTIGEN".</t>
+          <t>Representation of findings in the Microbiology Specimen domain should be handled as follows:</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>MB-A1b</t>
+          <t>MB-A1a</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1b</t>
+          <t>1a</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2523,21 +2523,21 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>MBTESTCD; MBTEST; MBORRES</t>
+          <t>MBTEST; MBTSTDTL</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>For non-targeted identification of organisms (i.e., tests that have the ability to identify a range of organisms without specifically targeting any), the value for MBTESTCD/MBTEST should be "MCORGIDN"/"Microbial Organism Identification", and the result should be the name of the organism or group of organisms found to be present (e.g., "INFLUENZA A VIRUS SUBTYPE H1N1"; "CLONORCHIS SINENSIS"). In this scenario MBORRES is populated with values from the Microorganism Codelist (C85491).</t>
+          <t>In cases of tests that target an organism, group of organisms, or antigen for identification, MBTEST equals the name of the organism/antigen targeted by the identification assay, and i. MBTSTDTL should be “DETECTION”. ii. The result should generally be "PRESENT"/"ABSENT", "POSITIVE"/"NEGATIVE", or "INDETERMINATE". However, there may be cases where a test differentiates between 2 or more similar organisms, in which case it would be appropriate for the result to be the name of the organism detected. For example, a test may look for influenza A or influenza B antigen. In this case, MBTEST would be "Influenza A/B Antigen"; the result could be "INFLUENZA A ANTIGEN", "INFLUENZA B ANTIGEN", or "INFLUENZA A/B ANTIGEN".</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PCTESTCD-Notes</t>
+          <t>MB-A1b</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2552,33 +2552,41 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Variable table, CDISC Notes</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>6.3.5.7.1 Microbiology Specimen (MB); MB – Assumptions</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>1b</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>PCTESTCD</t>
+          <t>MBTESTCD; MBTEST; MBORRES</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
+          <t>For non-targeted identification of organisms (i.e., tests that have the ability to identify a range of organisms without specifically targeting any), the value for MBTESTCD/MBTEST should be "MCORGIDN"/"Microbial Organism Identification", and the result should be the name of the organism or group of organisms found to be present (e.g., "INFLUENZA A VIRUS SUBTYPE H1N1"; "CLONORCHIS SINENSIS"). In this scenario MBORRES is populated with values from the Microorganism Codelist (C85491).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PCTEST-Notes</t>
+          <t>PCTESTCD-Notes</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2605,21 +2613,21 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>PCTEST</t>
+          <t>PCTESTCD</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
+          <t>Short name of the analyte or specimen characteristic. It can be used as a column name when converting a dataset from a vertical to a horizontal format. The value in PCTESTCD cannot be longer than 8 characters, nor can it start with a number (e.g., "1TEST" is not valid). PCTESTCD cannot contain characters other than letters, numbers, or underscores. Examples: "ASA", "VOL", "SPG".</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>RS-DR-A1</t>
+          <t>PCTEST-Notes</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2634,41 +2642,33 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
+          <t>Variable table, CDISC Notes</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>RSCAT</t>
+          <t>PCTEST</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>RSCAT is used to group a set of assessments based on a disease response criterion (published or protocol-defined). One of the codelists for RSCAT is ONCRSCAT. The ONCRSCAT codelist contains controlled terminology for oncology disease response assessments.</t>
+          <t>Name of the analyte or specimen characteristic. Note any test normally performed by a clinical laboratory is considered a lab test. The value in PCTEST cannot be longer than 40 characters. Examples: "Acetylsalicylic Acid", "Volume", "Specific Gravity".</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>RS-DR-A6b</t>
+          <t>RS-DR-A1</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>6b</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>332</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2710,14 +2710,14 @@
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>If the criteria used to determine the response is unknown or not collected, this is represented as RSCAT = "UNSPECIFIED".</t>
+          <t>RSCAT is used to group a set of assessments based on a disease response criterion (published or protocol-defined). One of the codelists for RSCAT is ONCRSCAT. The ONCRSCAT codelist contains controlled terminology for oncology disease response assessments.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>RS-DR-A9</t>
+          <t>RS-DR-A6b</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6b</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>333</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2752,25 +2752,21 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>RSTEST; RSCAT</t>
+          <t>RSCAT</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Disease recurrence can be represented in the RS domain using RSTEST = "Disease Recurrence Indicator" to indicate that there was an assessment of whether there was disease recurrence. The RSCAT = "PROTOCOL DEFINED RESPONSE CRITERIA" can be used to indicate that the response assessment of disease recurrence was based on protocol-specified criteria rather than published response criteria.</t>
+          <t>If the criteria used to determine the response is unknown or not collected, this is represented as RSCAT = "UNSPECIFIED".</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>RS-CC-A2</t>
+          <t>RS-DR-A9</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2785,17 +2781,17 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>6.3.9.3.2 Clinical Classifications Use Case; RS – Clinical Classifications Use Case Assumptions</t>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2805,26 +2801,30 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>RSCAT</t>
+          <t>RSTEST; RSCAT</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>RSCAT is used to group a set of assessments based on a clinical classification. One of the codelists for RSCAT is CCCAT. The CCCAT codelist contains CDISC Controlled Terminology for clinical classifications instruments.</t>
+          <t>Disease recurrence can be represented in the RS domain using RSTEST = "Disease Recurrence Indicator" to indicate that there was an assessment of whether there was disease recurrence. The RSCAT = "PROTOCOL DEFINED RESPONSE CRITERIA" can be used to indicate that the response assessment of disease recurrence was based on protocol-specified criteria rather than published response criteria.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>RS-DR-A7</t>
+          <t>RS-CC-A2</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>routing</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
+          <t>6.3.9.3.2 Clinical Classifications Use Case; RS – Clinical Classifications Use Case Assumptions</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>336</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2854,21 +2854,21 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>RSEVALID; RSEVAL</t>
+          <t>RSCAT</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>The evaluator identifier variable (RSEVALID) can be used in conjunction with RSEVAL to provide additional detail of who is providing the assessment. For example, RSEVAL = "INDEPENDENT ASSESSOR" and RSEVALID = "RADIOLOGIST 1" may further qualify the RSEVALID variable. RSEVALID may be subject to controlled terminology but may also represent free text values depending on the use case. When used with disease response data, RSEVALID is subject to MEDEVAL controlled terminology.</t>
+          <t>RSCAT is used to group a set of assessments based on a clinical classification. One of the codelists for RSCAT is CCCAT. The CCCAT codelist contains CDISC Controlled Terminology for clinical classifications instruments.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>QS-A8</t>
+          <t>RS-DR-A7</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2883,37 +2883,41 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>6.3.9.2 Questionnaires (QS); QS – Assumptions</t>
+          <t>6.3.9.3.1 Disease Response Use Case; RS – Disease Response Use Case Assumptions</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>333</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>RSEVALID; RSEVAL</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>--EVAL and --EVALID must not be used to model QRS data in SDTM. These variables have had various interpretations on QRS CRFs and were used to represent a multitude of evaluator information about QRS instruments. This has made it more difficult for users of SDTM QRS data to interpret this data and more difficult to pool data for analyses. If needed, supplemental qualifiers may be used to represent this data. Updated information on a proposed solution to this issue will be posted on the CDISC QRS webpage (https://www.cdisc.org/standards/foundational/qrs).</t>
+          <t>The evaluator identifier variable (RSEVALID) can be used in conjunction with RSEVAL to provide additional detail of who is providing the assessment. For example, RSEVAL = "INDEPENDENT ASSESSOR" and RSEVALID = "RADIOLOGIST 1" may further qualify the RSEVALID variable. RSEVALID may be subject to controlled terminology but may also represent free text values depending on the use case. When used with disease response data, RSEVALID is subject to MEDEVAL controlled terminology.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TR-A1</t>
+          <t>QS-A8</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2928,45 +2932,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>6.3.12.2 Tumor/Lesion Results (TR); TR – Assumptions</t>
+          <t>6.3.9.2 Questionnaires (QS); QS – Assumptions</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>TR</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>TRLNKID</t>
-        </is>
-      </c>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>TR; TU</t>
-        </is>
-      </c>
+      <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>TRLNKID is used to relate records in the TR domain to an identification record in TU domain. The organization of data across the TU and TR domains requires a RELREC relationship to link the related data rows. A dataset-to-dataset link would be the most appropriate linking mechanism. Utilizing 1 of the existing ID variables is not possible, because --GRPID, --REFID, and --SPID may be used for other purposes, per the SDTM. The --LNKID variable is used for values that support a RELREC dataset-to-dataset relationship and to provide a unique code for each identified tumor/lesion/location of interest.</t>
+          <t>--EVAL and --EVALID must not be used to model QRS data in SDTM. These variables have had various interpretations on QRS CRFs and were used to represent a multitude of evaluator information about QRS instruments. This has made it more difficult for users of SDTM QRS data to interpret this data and more difficult to pool data for analyses. If needed, supplemental qualifiers may be used to represent this data. Updated information on a proposed solution to this issue will be posted on the CDISC QRS webpage (https://www.cdisc.org/standards/foundational/qrs).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TR-A2</t>
+          <t>TR-A1</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2986,7 +2982,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3001,23 +2997,76 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>TRLNKGRP</t>
+          <t>TRLNKID</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
+          <t>TR; TU</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKID is used to relate records in the TR domain to an identification record in TU domain. The organization of data across the TU and TR domains requires a RELREC relationship to link the related data rows. A dataset-to-dataset link would be the most appropriate linking mechanism. Utilizing 1 of the existing ID variables is not possible, because --GRPID, --REFID, and --SPID may be used for other purposes, per the SDTM. The --LNKID variable is used for values that support a RELREC dataset-to-dataset relationship and to provide a unique code for each identified tumor/lesion/location of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>TR-A2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 (2021-11-29)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>6.3.12.2 Tumor/Lesion Results (TR); TR – Assumptions</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>TRLNKGRP</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
           <t>TR; RS</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>TRLNKGRP is used to relate records in the TR domain to a response assessment record in the RS domain. The organization of data across the TR and RS domains requires a RELREC relationship to link the related data rows. A dataset-to-dataset link would be the most appropriate linking mechanism. Utilizing 1 of the existing ID variables is not possible because --GRPID, --REFID, and --SPID may be used for other purposes, per the SDTM. The --LNKGRP variable is used for values that support a RELREC dataset-to-dataset relationship and to provide a unique code for each response and associated tumor/lesion measurements/assessments.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
+  <autoFilter ref="A1:K46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5910,7 +5959,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31 22:14</t>
+          <t>2026-11-01 09:42</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5983,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -5958,7 +6007,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1b72ffa81f9f4bf123a5f0e5e182a6f8cd5313f5e70bd8e9c0ab2c97ae760da7</t>
+          <t>2271ba317b05df2d6124c67f5c5317f357b1d542ad021c46c1466d67c5e721da</t>
         </is>
       </c>
     </row>

--- a/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTMIG_Statements.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -695,179 +695,183 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>The IG refers to the CDISC CT Rules for some choices (e.g. IS-A7: when to use each of the two ISBDAGNT</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  codelists). The CT supplemental files -- Rules documents and Codetable Mapping files, listed on the</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Statements — one row per quoted statement.</t>
+          <t xml:space="preserve">  cdisc.org Controlled Terminology page -- are not read here. They may refine the statements quoted.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Variables — one row per variable in Variables_Named: the SDTMIG v3.4 variable-table row as published,</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  plus Named_In. An empty CDISC CT Codelist Code(s) means the table gives no codelist (e.g. PCTESTCD).</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>SHEETS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Provenance — versions; per sheet rows, columns and a content hash.</t>
+          <t>Statements — one row per quoted statement.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Variables — one row per variable in Variables_Named: the SDTMIG v3.4 variable-table row as published,</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMNS — Statements</t>
+          <t xml:space="preserve">  plus Named_In. An empty CDISC CT Codelist Code(s) means the table gives no codelist (e.g. PCTESTCD).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Statement_ID: domain + A + assumption item (+ sub-item), e.g. IS-A7b; 4.1.9-n for the §4.1.9 passages in</t>
+          <t>Provenance — versions; per sheet rows, columns and a content hash.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  order; &lt;variable&gt;-Notes for CDISC Notes. RS-DR = RS Disease Response Use Case Assumptions;</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  RS-CC = RS Clinical Classifications Use Case Assumptions.</t>
+          <t>COLUMNS — Statements</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Selected_As: facet | routing | record — why the row was selected.</t>
+          <t>Statement_ID: domain + A + assumption item (+ sub-item), e.g. IS-A7b; 4.1.9-n for the §4.1.9 passages in</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Source: the document and its date.</t>
+          <t xml:space="preserve">  order; &lt;variable&gt;-Notes for CDISC Notes. RS-DR = RS Disease Response Use Case Assumptions;</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Section: the numbered IG section; for Assumptions also the Assumptions heading.</t>
+          <t xml:space="preserve">  RS-CC = RS Clinical Classifications Use Case Assumptions.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Item: assumption item and lettered sub-item. An item row holds the item's text before its first sub-item;</t>
+          <t>Selected_As: facet | routing | record — why the row was selected.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a sub-item row keeps its roman sub-items (e.g. 1c holds i-iv).</t>
+          <t>Source: the document and its date.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Page: page in the IG (printed page = PDF page). Empty for CDISC Notes (CSV).</t>
+          <t>Section: the numbered IG section; for Assumptions also the Assumptions heading.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Domain: the dataset whose Assumptions or Notes the text belongs to; empty for §4.1.9.</t>
+          <t>Item: assumption item and lettered sub-item. An item row holds the item's text before its first sub-item;</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Variables_Named: words that are variables of the dataset their first two letters name, in the SDTMIG v3.4</t>
+          <t xml:space="preserve">  a sub-item row keeps its roman sub-items (e.g. 1c holds i-iv).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  variable table; in order of first appearance.</t>
+          <t>Page: page in the IG (printed page = PDF page). Empty for CDISC Notes (CSV).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Model_Variables_Named: words not in that dataset's SDTMIG v3.4 table whose -- form is an SDTM v2.0 variable</t>
+          <t>Domain: the dataset whose Assumptions or Notes the text belongs to; empty for §4.1.9.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of the dataset's observation class (e.g. LBPOS and LBLOC in LB-A8: --POS and --LOC, Findings).</t>
+          <t>Variables_Named: words that are variables of the dataset their first two letters name, in the SDTMIG v3.4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Domains_Named: dataset codes written as (XX) or "XX domain"; in order of first appearance.</t>
+          <t xml:space="preserve">  variable table; in order of first appearance.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Text: the statement, verbatim.</t>
+          <t>Model_Variables_Named: words not in that dataset's SDTMIG v3.4 table whose -- form is an SDTM v2.0 variable</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of the dataset's observation class (e.g. LBPOS and LBLOC in LB-A8: --POS and --LOC, Findings).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>COLUMNS — Variables</t>
+          <t>Domains_Named: dataset codes written as (XX) or "XX domain"; in order of first appearance.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>The columns of SDTMIG_v3.4.csv, unchanged, plus Named_In: the Statement_IDs that name the variable.</t>
+          <t>Text: the statement, verbatim.</t>
         </is>
       </c>
     </row>
@@ -875,14 +879,31 @@
       <c r="A61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>READING</t>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>COLUMNS — Variables</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>The columns of SDTMIG_v3.4.csv, unchanged, plus Named_In: the Statement_IDs that name the variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>READING</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Read with keep_default_na=False (pandas) or the equivalent, so that no cell is read as missing.</t>
         </is>
